--- a/test_wb_export.xlsx
+++ b/test_wb_export.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,26 +457,16 @@
           <t>Цена до скидки</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Скидка</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Ставка НДС</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SKU-001</t>
+          <t>SPORT-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>240151303</t>
+          <t>300151303</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,49 +476,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>TestBrand</t>
+          <t>SportLine</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Платье женское летнее хлопковое с карманами размер 44-56</t>
+          <t>Протеин сывороточный концентрат 80% 1 кг шоколад</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Платья</t>
+          <t>Спортивное питание</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2499</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4999</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>20%</t>
+          <t>3799</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SKU-002</t>
+          <t>KITCH-002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>240151304</t>
+          <t>300151304</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -538,49 +518,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TestBrand</t>
+          <t>KitchenPro</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Футболка мужская хлопок 100% оверсайз</t>
+          <t>Сковорода антипригарная с мраморным покрытием 28 см</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Футболки</t>
+          <t>Посуда и кухня</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>2499</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>20%</t>
+          <t>4999</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SKU-003</t>
+          <t>TOYS-003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>240151305</t>
+          <t>300151305</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -590,17 +560,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TestBrand</t>
+          <t>BrickMaster</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Кроссовки детские дышащие для бега</t>
+          <t>Конструктор LEGO-совместимый 500 деталей город</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Кроссовки</t>
+          <t>Игрушки</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -613,14 +583,88 @@
           <t>2999</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>47%</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>20%</t>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TECH-004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>300151306</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4601234567893</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SmartHome</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Умная колонка с голосовым помощником Алиса черная</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Электроника</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>4999</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>7999</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>HOME-005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>300151307</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4601234567894</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CozyHouse</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Плед флисовый двусторонний 200x220 см серый</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Товары для дома</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1299</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2599</t>
         </is>
       </c>
     </row>
